--- a/data/trans_dic/P19C01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 46,1</t>
+          <t>36,02; 46,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,61; 49,78</t>
+          <t>39,55; 50,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,42; 58,27</t>
+          <t>47,63; 58,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,63; 76,64</t>
+          <t>58,81; 76,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,63; 52,53</t>
+          <t>42,7; 52,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,32; 50,66</t>
+          <t>40,74; 51,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,38; 58,84</t>
+          <t>48,49; 59,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,5; 80,22</t>
+          <t>66,65; 79,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,19; 48,27</t>
+          <t>40,72; 47,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,85; 49,07</t>
+          <t>41,81; 49,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,36; 56,91</t>
+          <t>49,35; 57,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,72; 76,15</t>
+          <t>64,66; 76,22</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,12; 37,04</t>
+          <t>28,41; 36,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,44; 38,32</t>
+          <t>30,28; 38,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,67; 44,94</t>
+          <t>35,72; 44,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,62; 71,69</t>
+          <t>59,47; 70,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,29; 42,78</t>
+          <t>34,53; 42,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,49; 45,31</t>
+          <t>36,86; 45,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,28; 49,09</t>
+          <t>40,55; 49,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,97; 80,62</t>
+          <t>64,03; 81,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 38,72</t>
+          <t>32,74; 38,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,59; 40,69</t>
+          <t>34,62; 40,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,15; 45,79</t>
+          <t>39,57; 45,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,95; 76,14</t>
+          <t>63,73; 75,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 34,59</t>
+          <t>25,75; 34,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,46; 34,44</t>
+          <t>26,76; 34,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,46; 45,36</t>
+          <t>36,37; 44,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,85; 65,15</t>
+          <t>55,99; 64,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,9; 35,66</t>
+          <t>27,91; 35,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,26; 41,75</t>
+          <t>34,18; 41,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,51; 51,01</t>
+          <t>42,68; 51,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,31; 66,21</t>
+          <t>59,24; 66,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,11; 33,71</t>
+          <t>27,91; 33,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,76; 37,18</t>
+          <t>31,82; 37,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,24; 47,07</t>
+          <t>40,82; 46,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,88; 64,62</t>
+          <t>58,73; 64,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,45; 30,56</t>
+          <t>21,71; 30,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 30,28</t>
+          <t>22,51; 30,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,59; 46,47</t>
+          <t>37,38; 46,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,43; 61,6</t>
+          <t>19,42; 61,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,77; 33,47</t>
+          <t>24,88; 33,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,83; 38,51</t>
+          <t>30,41; 38,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,83; 48,33</t>
+          <t>39,27; 48,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,75; 62,8</t>
+          <t>49,16; 62,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,31; 30,48</t>
+          <t>24,57; 30,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 33,2</t>
+          <t>27,02; 33,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 46,06</t>
+          <t>39,53; 45,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 60,6</t>
+          <t>29,61; 60,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,93; 31,85</t>
+          <t>20,96; 31,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,88; 30,58</t>
+          <t>20,82; 30,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,88; 41,69</t>
+          <t>31,07; 40,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,74; 55,63</t>
+          <t>47,56; 55,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,52; 26,31</t>
+          <t>17,26; 26,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,81; 32,9</t>
+          <t>22,96; 32,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 44,76</t>
+          <t>34,41; 44,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,25; 59,5</t>
+          <t>53,13; 59,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,32</t>
+          <t>20,27; 27,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,11; 29,81</t>
+          <t>23,33; 29,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,7; 41,41</t>
+          <t>34,17; 41,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,28; 56,47</t>
+          <t>51,37; 56,23</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,44; 27,73</t>
+          <t>16,76; 27,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,51; 22,27</t>
+          <t>12,57; 22,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,37; 42,35</t>
+          <t>29,84; 42,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,53; 54,18</t>
+          <t>45,69; 54,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,06; 25,09</t>
+          <t>15,67; 25,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,74; 27,86</t>
+          <t>18,12; 27,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,78; 41,22</t>
+          <t>28,91; 40,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 53,27</t>
+          <t>13,96; 53,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,35; 24,87</t>
+          <t>17,34; 24,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,09; 23,96</t>
+          <t>16,72; 23,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,71; 39,38</t>
+          <t>30,83; 39,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,2; 51,71</t>
+          <t>20,87; 51,9</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 25,62</t>
+          <t>11,85; 25,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,85</t>
+          <t>9,34; 20,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,49; 37,49</t>
+          <t>23,55; 36,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,05; 46,74</t>
+          <t>36,81; 46,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 22,14</t>
+          <t>10,96; 22,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,3; 24,93</t>
+          <t>15,11; 24,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,38; 39,48</t>
+          <t>25,79; 39,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,17; 44,67</t>
+          <t>37,79; 44,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,1</t>
+          <t>12,94; 21,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,94; 20,95</t>
+          <t>14,07; 21,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,57; 37,06</t>
+          <t>27,0; 36,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,51; 44,54</t>
+          <t>38,58; 44,2</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,17; 31,6</t>
+          <t>27,99; 31,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,58; 31,25</t>
+          <t>27,78; 31,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,95; 42,93</t>
+          <t>38,77; 42,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41,03; 58,15</t>
+          <t>41,74; 58,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,68; 33,38</t>
+          <t>29,71; 33,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,54; 36,01</t>
+          <t>32,55; 35,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,56; 45,32</t>
+          <t>41,61; 45,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,31; 60,07</t>
+          <t>44,37; 60,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,41; 31,95</t>
+          <t>29,36; 31,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,56; 33,11</t>
+          <t>30,74; 33,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40,75; 43,45</t>
+          <t>40,83; 43,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,86; 58,51</t>
+          <t>48,01; 57,99</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>129286; 165677</t>
+          <t>129467; 166003</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>150197; 188749</t>
+          <t>149947; 189586</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167318; 205584</t>
+          <t>168065; 205616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224799; 293858</t>
+          <t>225491; 293257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>160402; 197659</t>
+          <t>160674; 198316</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>149573; 187939</t>
+          <t>151137; 189358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>170257; 207078</t>
+          <t>170640; 207984</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>201844; 243486</t>
+          <t>202308; 241643</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303024; 355095</t>
+          <t>299541; 352109</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313955; 368134</t>
+          <t>313681; 368422</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347855; 401074</t>
+          <t>347814; 403157</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>444612; 523148</t>
+          <t>444226; 523616</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>168100; 213828</t>
+          <t>164030; 212682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181823; 228888</t>
+          <t>180831; 230383</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175864; 221613</t>
+          <t>176115; 220352</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>239872; 288437</t>
+          <t>239298; 285621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>187819; 234323</t>
+          <t>189116; 233666</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>204280; 253694</t>
+          <t>206378; 255961</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>200093; 243823</t>
+          <t>201421; 245046</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>319673; 402876</t>
+          <t>319963; 408650</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>369550; 435651</t>
+          <t>368378; 433919</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>400260; 470804</t>
+          <t>400601; 467649</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>387472; 453277</t>
+          <t>391643; 450353</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>576812; 686770</t>
+          <t>574884; 680678</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>131262; 173971</t>
+          <t>129492; 171141</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>155236; 202039</t>
+          <t>156979; 200814</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>203380; 253066</t>
+          <t>202913; 250361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>292689; 341433</t>
+          <t>293402; 339275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>168373; 215216</t>
+          <t>168436; 215735</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>225590; 274883</t>
+          <t>225030; 274534</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>243604; 292339</t>
+          <t>244584; 292833</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>315481; 352185</t>
+          <t>315069; 351769</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>311054; 372979</t>
+          <t>308870; 373190</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>395472; 462957</t>
+          <t>396215; 461995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>466411; 532354</t>
+          <t>461594; 528232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>621708; 682292</t>
+          <t>620165; 682199</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86827; 123696</t>
+          <t>87870; 123994</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120298; 164385</t>
+          <t>122220; 167037</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192618; 238111</t>
+          <t>191546; 238649</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>159011; 531575</t>
+          <t>167563; 531250</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>108769; 146988</t>
+          <t>109276; 147128</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167704; 216539</t>
+          <t>170990; 216715</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>217008; 263338</t>
+          <t>213984; 261652</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>334556; 439975</t>
+          <t>344438; 440407</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>205200; 257223</t>
+          <t>207319; 260937</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>303195; 366884</t>
+          <t>298575; 365435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>420994; 486940</t>
+          <t>417970; 485642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>470570; 947566</t>
+          <t>462908; 950973</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57016; 86754</t>
+          <t>57077; 85510</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75456; 110472</t>
+          <t>75224; 109328</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114563; 154675</t>
+          <t>115274; 150656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>260964; 304080</t>
+          <t>259960; 303635</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55908; 83950</t>
+          <t>55079; 83412</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89129; 128534</t>
+          <t>89694; 127373</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>134154; 177195</t>
+          <t>136201; 177851</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>284610; 318049</t>
+          <t>283967; 318440</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119969; 161577</t>
+          <t>119855; 160901</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173777; 224166</t>
+          <t>175445; 224491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258444; 317582</t>
+          <t>262067; 317783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>554407; 610517</t>
+          <t>555315; 607915</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34974; 58999</t>
+          <t>35663; 58517</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32839; 58448</t>
+          <t>32988; 58970</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67591; 97460</t>
+          <t>68677; 97346</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>163604; 194705</t>
+          <t>164206; 194107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37057; 61723</t>
+          <t>38552; 61985</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53336; 83745</t>
+          <t>54453; 83235</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79702; 114149</t>
+          <t>80074; 112574</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>80414; 319582</t>
+          <t>83771; 319185</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79613; 114097</t>
+          <t>79555; 113083</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96206; 134886</t>
+          <t>94137; 133773</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155723; 199662</t>
+          <t>156347; 198868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>203396; 496048</t>
+          <t>200162; 497855</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15051; 32474</t>
+          <t>15020; 32605</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16062; 36709</t>
+          <t>17265; 37135</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34550; 55128</t>
+          <t>34626; 54322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102353; 129098</t>
+          <t>101685; 128304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23646; 46088</t>
+          <t>22811; 46073</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46271; 75397</t>
+          <t>45695; 74546</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57824; 89968</t>
+          <t>58769; 91097</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>155984; 182560</t>
+          <t>154432; 183441</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42223; 70673</t>
+          <t>43332; 72930</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67930; 102121</t>
+          <t>68559; 103058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99627; 138960</t>
+          <t>101238; 136424</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>263765; 305080</t>
+          <t>264250; 302704</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>692031; 776288</t>
+          <t>687407; 777003</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>803968; 910699</t>
+          <t>809706; 913371</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1037677; 1143813</t>
+          <t>1032978; 1137089</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1376402; 1951046</t>
+          <t>1400399; 1951534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>813224; 914498</t>
+          <t>813931; 907265</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1023560; 1132517</t>
+          <t>1023692; 1131777</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1191683; 1299392</t>
+          <t>1193046; 1302499</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1585742; 2149709</t>
+          <t>1587861; 2147506</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1528215; 1660205</t>
+          <t>1525596; 1658507</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1851991; 2006171</t>
+          <t>1863103; 2017148</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2254138; 2403527</t>
+          <t>2258370; 2401253</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3318150; 4056925</t>
+          <t>3328718; 4020537</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,02; 46,19</t>
+          <t>35,55; 46,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,55; 50,0</t>
+          <t>39,88; 50,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,63; 58,27</t>
+          <t>47,68; 57,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,81; 76,48</t>
+          <t>57,85; 73,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,7; 52,71</t>
+          <t>42,17; 52,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,74; 51,04</t>
+          <t>40,62; 50,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,49; 59,1</t>
+          <t>48,59; 58,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,65; 79,61</t>
+          <t>64,98; 78,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,72; 47,86</t>
+          <t>40,76; 48,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,81; 49,11</t>
+          <t>41,55; 48,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,35; 57,2</t>
+          <t>49,63; 57,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,66; 76,22</t>
+          <t>63,36; 74,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,41; 36,84</t>
+          <t>28,86; 37,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 38,57</t>
+          <t>30,64; 38,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,72; 44,69</t>
+          <t>35,66; 44,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,47; 70,99</t>
+          <t>59,1; 71,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,53; 42,66</t>
+          <t>34,56; 42,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,86; 45,72</t>
+          <t>36,72; 45,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,55; 49,33</t>
+          <t>40,52; 48,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64,03; 81,78</t>
+          <t>60,35; 69,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,74; 38,57</t>
+          <t>33,1; 38,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 40,41</t>
+          <t>34,55; 40,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,57; 45,5</t>
+          <t>39,38; 45,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,73; 75,46</t>
+          <t>61,72; 69,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,75; 34,03</t>
+          <t>25,89; 34,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,76; 34,23</t>
+          <t>26,47; 34,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 44,88</t>
+          <t>36,6; 44,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,99; 64,74</t>
+          <t>55,64; 63,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,91; 35,74</t>
+          <t>27,8; 35,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,18; 41,69</t>
+          <t>34,14; 41,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,68; 51,1</t>
+          <t>42,51; 51,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,24; 66,14</t>
+          <t>59,89; 66,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,91; 33,73</t>
+          <t>28,22; 33,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,82; 37,1</t>
+          <t>31,73; 37,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,82; 46,71</t>
+          <t>40,99; 46,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,73; 64,61</t>
+          <t>58,77; 64,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,71; 30,63</t>
+          <t>21,74; 30,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,51; 30,77</t>
+          <t>22,49; 30,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,38; 46,58</t>
+          <t>37,41; 46,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 61,56</t>
+          <t>55,69; 63,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,88; 33,5</t>
+          <t>24,83; 33,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 38,54</t>
+          <t>29,64; 38,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,27; 48,02</t>
+          <t>39,66; 48,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,16; 62,86</t>
+          <t>58,85; 64,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,57; 30,92</t>
+          <t>24,42; 30,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,02; 33,07</t>
+          <t>27,42; 33,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,53; 45,93</t>
+          <t>39,92; 46,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,61; 60,82</t>
+          <t>58,17; 63,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,96; 31,4</t>
+          <t>20,98; 31,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,82; 30,26</t>
+          <t>20,82; 30,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,07; 40,61</t>
+          <t>30,52; 41,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,56; 55,55</t>
+          <t>47,8; 55,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,26; 26,14</t>
+          <t>17,63; 26,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,96; 32,6</t>
+          <t>23,39; 32,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,41; 44,93</t>
+          <t>33,98; 44,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,13; 59,57</t>
+          <t>53,22; 59,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,27; 27,21</t>
+          <t>20,42; 26,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,33; 29,85</t>
+          <t>23,14; 29,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,17; 41,44</t>
+          <t>34,11; 41,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,37; 56,23</t>
+          <t>51,47; 56,54</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,76; 27,5</t>
+          <t>16,29; 27,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,47</t>
+          <t>12,36; 22,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,84; 42,3</t>
+          <t>29,29; 42,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,69; 54,02</t>
+          <t>45,87; 54,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,67; 25,2</t>
+          <t>15,34; 24,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,12; 27,69</t>
+          <t>18,6; 28,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,91; 40,65</t>
+          <t>28,44; 40,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 53,21</t>
+          <t>49,45; 56,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,34; 24,65</t>
+          <t>17,55; 24,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,72; 23,76</t>
+          <t>16,68; 23,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,83; 39,22</t>
+          <t>31,2; 39,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,87; 51,9</t>
+          <t>49,07; 54,26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 25,72</t>
+          <t>11,69; 25,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 20,08</t>
+          <t>8,88; 19,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,55; 36,94</t>
+          <t>24,27; 37,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,81; 46,45</t>
+          <t>37,25; 46,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,96; 22,13</t>
+          <t>11,11; 22,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,11; 24,65</t>
+          <t>15,49; 25,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,79; 39,98</t>
+          <t>25,77; 39,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,79; 44,89</t>
+          <t>38,43; 45,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,94; 21,77</t>
+          <t>13,19; 21,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,07; 21,15</t>
+          <t>14,15; 20,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,0; 36,39</t>
+          <t>26,65; 36,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,58; 44,2</t>
+          <t>39,26; 45,08</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,99; 31,63</t>
+          <t>27,98; 31,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,78; 31,34</t>
+          <t>27,62; 31,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,77; 42,68</t>
+          <t>38,88; 42,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41,74; 58,17</t>
+          <t>55,08; 58,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,11</t>
+          <t>29,66; 33,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,55; 35,98</t>
+          <t>32,42; 36,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,61; 45,43</t>
+          <t>41,39; 45,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,37; 60,01</t>
+          <t>57,68; 60,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,36; 31,92</t>
+          <t>29,28; 31,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,74; 33,29</t>
+          <t>30,77; 33,3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40,83; 43,41</t>
+          <t>40,78; 43,59</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,01; 57,99</t>
+          <t>56,82; 59,28</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261780</t>
+          <t>250515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>223902</t>
+          <t>249728</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>485682</t>
+          <t>500243</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>129467; 166003</t>
+          <t>127751; 165529</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>149947; 189586</t>
+          <t>151220; 189758</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168065; 205616</t>
+          <t>168225; 204310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>225491; 293257</t>
+          <t>219159; 280205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>160674; 198316</t>
+          <t>158683; 198202</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151137; 189358</t>
+          <t>150691; 188304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>170640; 207984</t>
+          <t>170987; 207016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>202308; 241643</t>
+          <t>223049; 270248</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299541; 352109</t>
+          <t>299833; 354822</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313681; 368422</t>
+          <t>311694; 365340</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347814; 403157</t>
+          <t>349754; 403475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>444226; 523616</t>
+          <t>457484; 537337</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263659</t>
+          <t>292609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>352477</t>
+          <t>313392</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>616136</t>
+          <t>606001</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164030; 212682</t>
+          <t>166613; 213578</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>180831; 230383</t>
+          <t>182995; 229122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176115; 220352</t>
+          <t>175812; 218951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>239298; 285621</t>
+          <t>263531; 319958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>189116; 233666</t>
+          <t>189301; 232190</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>206378; 255961</t>
+          <t>205554; 254082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>201421; 245046</t>
+          <t>201256; 243006</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>319963; 408650</t>
+          <t>291265; 334205</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>368378; 433919</t>
+          <t>372355; 434769</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>400601; 467649</t>
+          <t>399792; 470864</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>391643; 450353</t>
+          <t>389774; 451356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>574884; 680678</t>
+          <t>573049; 645084</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317136</t>
+          <t>360161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>334940</t>
+          <t>383579</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>652076</t>
+          <t>743739</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>129492; 171141</t>
+          <t>130232; 172386</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>156979; 200814</t>
+          <t>155296; 200721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202913; 250361</t>
+          <t>204187; 250088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>293402; 339275</t>
+          <t>334452; 383603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>168436; 215735</t>
+          <t>167808; 215500</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>225030; 274534</t>
+          <t>224823; 276117</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>244584; 292833</t>
+          <t>243594; 294365</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>315069; 351769</t>
+          <t>363687; 403280</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>308870; 373190</t>
+          <t>312267; 372822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>396215; 461995</t>
+          <t>395095; 463810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>461594; 528232</t>
+          <t>463589; 528206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>620165; 682199</t>
+          <t>710145; 776245</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373589</t>
+          <t>402386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>411195</t>
+          <t>447851</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>784783</t>
+          <t>850237</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87870; 123994</t>
+          <t>87993; 124219</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122220; 167037</t>
+          <t>122094; 165201</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>191546; 238649</t>
+          <t>191691; 238994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167563; 531250</t>
+          <t>377745; 431782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>109276; 147128</t>
+          <t>109071; 147758</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>170990; 216715</t>
+          <t>166662; 216150</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>213984; 261652</t>
+          <t>216124; 262168</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>344438; 440407</t>
+          <t>424775; 467833</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>207319; 260937</t>
+          <t>206069; 258181</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>298575; 365435</t>
+          <t>303012; 368293</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>417970; 485642</t>
+          <t>422068; 487257</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>462908; 950973</t>
+          <t>814440; 883396</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281785</t>
+          <t>306109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>300786</t>
+          <t>334921</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>582571</t>
+          <t>641030</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57077; 85510</t>
+          <t>57151; 87023</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75224; 109328</t>
+          <t>75229; 108702</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115274; 150656</t>
+          <t>113231; 152660</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>259960; 303635</t>
+          <t>283606; 330147</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55079; 83412</t>
+          <t>56262; 84211</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89694; 127373</t>
+          <t>91387; 126873</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>136201; 177851</t>
+          <t>134527; 175567</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>283967; 318440</t>
+          <t>317129; 353597</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119855; 160901</t>
+          <t>120765; 159654</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>175445; 224491</t>
+          <t>173993; 224974</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>262067; 317783</t>
+          <t>261561; 316178</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>555315; 607915</t>
+          <t>612111; 672409</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178306</t>
+          <t>199966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>205787</t>
+          <t>226231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>384093</t>
+          <t>426196</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35663; 58517</t>
+          <t>34650; 59065</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32988; 58970</t>
+          <t>32452; 58877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68677; 97346</t>
+          <t>67400; 97292</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>164206; 194107</t>
+          <t>182427; 215974</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38552; 61985</t>
+          <t>37742; 61220</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54453; 83235</t>
+          <t>55912; 84859</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80074; 112574</t>
+          <t>78777; 111382</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83771; 319185</t>
+          <t>212091; 241156</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79555; 113083</t>
+          <t>80511; 113798</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94137; 133773</t>
+          <t>93914; 132888</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>156347; 198868</t>
+          <t>158199; 200605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>200162; 497855</t>
+          <t>405625; 448513</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114956</t>
+          <t>127585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>168754</t>
+          <t>188094</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>283710</t>
+          <t>315679</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15020; 32605</t>
+          <t>14818; 32364</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17265; 37135</t>
+          <t>16426; 36580</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34626; 54322</t>
+          <t>35689; 55098</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101685; 128304</t>
+          <t>112996; 141706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22811; 46073</t>
+          <t>23128; 47299</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45695; 74546</t>
+          <t>46843; 76077</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58769; 91097</t>
+          <t>58735; 90567</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>154432; 183441</t>
+          <t>171308; 203446</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43332; 72930</t>
+          <t>44175; 72290</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68559; 103058</t>
+          <t>68943; 101952</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101238; 136424</t>
+          <t>99908; 136952</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>264250; 302704</t>
+          <t>294099; 337685</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1791211</t>
+          <t>1939330</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>2143796</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3789051</t>
+          <t>4083126</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>687407; 777003</t>
+          <t>687219; 780082</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>809706; 913371</t>
+          <t>805087; 907853</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1032978; 1137089</t>
+          <t>1035993; 1135352</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1400399; 1951534</t>
+          <t>1872035; 2002868</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>813931; 907265</t>
+          <t>812786; 908419</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1023692; 1131777</t>
+          <t>1019742; 1132844</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1193046; 1302499</t>
+          <t>1186673; 1299243</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1587861; 2147506</t>
+          <t>2091003; 2197801</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1525596; 1658507</t>
+          <t>1521653; 1660640</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1863103; 2017148</t>
+          <t>1864483; 2018008</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2258370; 2401253</t>
+          <t>2255915; 2411091</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3328718; 4020537</t>
+          <t>3990974; 4163549</t>
         </is>
       </c>
     </row>
